--- a/data/trans_dic/P19C03-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P19C03-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por un empaste</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por un empaste (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>31,03; 40,77</t>
+          <t>31,26; 41,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>28,95; 39,01</t>
+          <t>29,32; 39,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24,02; 34,4</t>
+          <t>23,9; 33,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,88; 30,79</t>
+          <t>14,12; 29,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,7; 38,11</t>
+          <t>28,7; 37,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,24; 34,52</t>
+          <t>24,86; 34,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,62; 29,89</t>
+          <t>21,1; 29,97</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,91; 23,85</t>
+          <t>11,16; 24,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>31,01; 38,07</t>
+          <t>31,42; 38,25</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28,13; 35,09</t>
+          <t>28,17; 35,05</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23,4; 30,53</t>
+          <t>23,48; 30,18</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,74; 25,09</t>
+          <t>14,33; 24,58</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>35,52; 43,61</t>
+          <t>35,38; 44,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30,64; 38,71</t>
+          <t>30,16; 38,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30,06; 38,59</t>
+          <t>29,7; 38,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18,19; 29,52</t>
+          <t>17,73; 28,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,19; 43,27</t>
+          <t>35,2; 44,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,9; 38,56</t>
+          <t>29,77; 37,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,24; 34,18</t>
+          <t>26,43; 34,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,74; 21,79</t>
+          <t>10,32; 21,57</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>37,03; 42,68</t>
+          <t>36,63; 42,74</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31,3; 36,98</t>
+          <t>31,3; 36,81</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29,29; 35,41</t>
+          <t>29,09; 35,0</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,01; 23,28</t>
+          <t>15,25; 23,34</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>34,18; 42,98</t>
+          <t>34,17; 43,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29,91; 37,95</t>
+          <t>29,64; 37,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29,54; 37,53</t>
+          <t>29,54; 38,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,61; 26,56</t>
+          <t>18,99; 26,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33,02; 41,25</t>
+          <t>32,98; 41,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31,89; 39,59</t>
+          <t>31,95; 39,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,45; 33,96</t>
+          <t>26,29; 33,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,37; 24,13</t>
+          <t>18,42; 24,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>35,05; 40,88</t>
+          <t>35,09; 40,94</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>31,97; 37,49</t>
+          <t>31,95; 37,42</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29,45; 34,72</t>
+          <t>29,24; 34,69</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>19,63; 24,09</t>
+          <t>19,33; 24,11</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>30,26; 39,97</t>
+          <t>30,67; 40,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28,73; 37,27</t>
+          <t>28,56; 37,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23,61; 31,71</t>
+          <t>23,54; 31,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,7; 23,05</t>
+          <t>7,03; 22,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>31,08; 39,36</t>
+          <t>30,6; 39,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,48; 34,84</t>
+          <t>26,51; 34,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,0; 32,95</t>
+          <t>24,72; 32,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19,54; 38,75</t>
+          <t>19,63; 35,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31,62; 38,56</t>
+          <t>31,8; 38,67</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28,89; 34,92</t>
+          <t>28,92; 34,79</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25,41; 31,23</t>
+          <t>25,66; 31,3</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,7; 24,72</t>
+          <t>11,65; 24,9</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,05; 26,03</t>
+          <t>15,86; 25,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>25,83; 36,03</t>
+          <t>25,98; 35,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,59; 26,03</t>
+          <t>16,56; 24,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,71; 23,4</t>
+          <t>16,16; 22,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,52; 35,8</t>
+          <t>25,23; 35,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,84; 37,12</t>
+          <t>26,9; 37,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,15; 29,63</t>
+          <t>19,65; 28,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,53; 23,62</t>
+          <t>18,49; 23,71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22,4; 29,67</t>
+          <t>22,27; 29,71</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27,64; 34,72</t>
+          <t>27,7; 35,08</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19,79; 25,72</t>
+          <t>19,91; 26,53</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,97; 22,27</t>
+          <t>17,95; 22,17</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,45; 16,92</t>
+          <t>8,65; 17,24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,26; 21,72</t>
+          <t>11,23; 21,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14,45; 23,97</t>
+          <t>14,43; 24,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10,43; 16,41</t>
+          <t>10,68; 16,49</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16,39; 25,55</t>
+          <t>15,75; 25,6</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,89; 24,77</t>
+          <t>15,97; 24,97</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17,51; 26,81</t>
+          <t>17,22; 27,15</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,71; 16,74</t>
+          <t>3,98; 16,84</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13,7; 20,68</t>
+          <t>13,59; 20,4</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15,18; 22,02</t>
+          <t>15,35; 22,23</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17,59; 24,53</t>
+          <t>17,32; 24,64</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,08; 15,36</t>
+          <t>5,96; 15,35</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,09; 11,34</t>
+          <t>2,17; 11,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,54; 12,73</t>
+          <t>4,51; 13,14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,53; 15,27</t>
+          <t>6,18; 15,41</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,68; 11,08</t>
+          <t>5,71; 10,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,72; 9,34</t>
+          <t>2,72; 9,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,23; 10,21</t>
+          <t>4,31; 10,08</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,59; 18,3</t>
+          <t>7,81; 18,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,08; 9,94</t>
+          <t>6,07; 9,73</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,17; 8,43</t>
+          <t>3,37; 8,76</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5,21; 10,12</t>
+          <t>5,03; 9,93</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8,28; 15,62</t>
+          <t>8,16; 15,3</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,45; 9,54</t>
+          <t>6,37; 9,59</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>30,08; 34,04</t>
+          <t>30,09; 33,87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>28,16; 31,77</t>
+          <t>28,27; 31,98</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25,65; 29,28</t>
+          <t>25,99; 29,39</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13,9; 20,19</t>
+          <t>13,8; 20,05</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>30,12; 33,87</t>
+          <t>30,36; 33,81</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,05; 30,57</t>
+          <t>27,43; 30,71</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,66; 27,87</t>
+          <t>24,69; 28,04</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>14,48; 19,96</t>
+          <t>14,53; 19,89</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>30,72; 33,28</t>
+          <t>30,82; 33,32</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28,31; 30,8</t>
+          <t>28,31; 30,67</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25,65; 28,05</t>
+          <t>25,61; 28,18</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>15,26; 19,35</t>
+          <t>15,51; 19,38</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por un empaste</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por un empaste (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>111505; 146535</t>
+          <t>112340; 149436</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>109496; 147562</t>
+          <t>110911; 148738</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>84739; 121372</t>
+          <t>84340; 119900</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>53211; 118063</t>
+          <t>54125; 114305</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>107984; 143407</t>
+          <t>108001; 142311</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>93628; 128051</t>
+          <t>92229; 126879</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>72585; 105179</t>
+          <t>74262; 105480</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>33116; 72409</t>
+          <t>33861; 73808</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>228107; 280062</t>
+          <t>231178; 281391</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>210739; 262884</t>
+          <t>211067; 262580</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>164890; 215172</t>
+          <t>165467; 212684</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>101277; 172372</t>
+          <t>98413; 168890</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>204541; 251075</t>
+          <t>203688; 254613</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>182711; 230849</t>
+          <t>179848; 226996</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>148214; 190281</t>
+          <t>146448; 189915</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>73192; 118780</t>
+          <t>71338; 115439</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>192756; 236980</t>
+          <t>192777; 241262</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>167082; 215462</t>
+          <t>166339; 212200</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>130362; 169794</t>
+          <t>131303; 171843</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>53656; 108860</t>
+          <t>51585; 107789</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>416022; 479529</t>
+          <t>411506; 480156</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>361598; 427151</t>
+          <t>361545; 425188</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>289932; 350520</t>
+          <t>287890; 346398</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>135386; 209989</t>
+          <t>137547; 210555</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>171542; 215731</t>
+          <t>171478; 217731</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>175175; 222310</t>
+          <t>173624; 220524</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>164802; 209393</t>
+          <t>164775; 212426</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>97327; 138912</t>
+          <t>99294; 139681</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>199271; 248950</t>
+          <t>199034; 250245</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>210317; 261107</t>
+          <t>210684; 261171</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>151582; 194633</t>
+          <t>150653; 193911</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>97699; 128338</t>
+          <t>97970; 128657</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>387410; 451887</t>
+          <t>387894; 452612</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>398100; 466836</t>
+          <t>397833; 465935</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>333028; 392650</t>
+          <t>330701; 392371</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>207041; 254092</t>
+          <t>203866; 254333</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>122464; 161781</t>
+          <t>124132; 163587</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>155958; 202295</t>
+          <t>155014; 201663</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>120952; 162450</t>
+          <t>120614; 162921</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>57850; 198912</t>
+          <t>60669; 198129</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>136517; 172877</t>
+          <t>134375; 175023</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>148668; 195585</t>
+          <t>148861; 194272</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>136232; 179517</t>
+          <t>134673; 178156</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>136923; 271460</t>
+          <t>137526; 251296</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>266814; 325444</t>
+          <t>268411; 326369</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>319031; 385633</t>
+          <t>319389; 384156</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>268674; 330221</t>
+          <t>271343; 330903</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>182928; 386440</t>
+          <t>182092; 389367</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>43708; 70899</t>
+          <t>43186; 70181</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>93343; 130191</t>
+          <t>93855; 128738</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>61552; 96560</t>
+          <t>61443; 92589</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>91342; 127924</t>
+          <t>88334; 123677</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>81422; 114237</t>
+          <t>80510; 112703</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>104865; 145049</t>
+          <t>105103; 145342</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>79750; 117316</t>
+          <t>77786; 114397</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>98918; 126093</t>
+          <t>98706; 126581</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>132477; 175478</t>
+          <t>131728; 175724</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>207827; 261091</t>
+          <t>208311; 263827</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>151778; 197272</t>
+          <t>152716; 203441</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>194206; 240578</t>
+          <t>193930; 239579</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>17976; 36003</t>
+          <t>18405; 36673</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>29558; 57023</t>
+          <t>29466; 55788</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>33245; 55165</t>
+          <t>33207; 57489</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>37480; 58953</t>
+          <t>38370; 59274</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>40465; 63091</t>
+          <t>38904; 63208</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>47618; 74200</t>
+          <t>47847; 74818</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>48495; 74253</t>
+          <t>47700; 75201</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>22234; 100416</t>
+          <t>23887; 101047</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>62971; 95051</t>
+          <t>62472; 93759</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>85306; 123768</t>
+          <t>86261; 124954</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>89199; 124365</t>
+          <t>87806; 124920</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>58350; 147323</t>
+          <t>57141; 147283</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2654; 14375</t>
+          <t>2745; 13965</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>8402; 23547</t>
+          <t>8345; 24306</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9600; 22456</t>
+          <t>9095; 22659</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15646; 30518</t>
+          <t>15732; 29024</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5664; 19446</t>
+          <t>5671; 19419</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12834; 30992</t>
+          <t>13073; 30581</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17305; 41708</t>
+          <t>17793; 43218</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>24854; 40615</t>
+          <t>24805; 39761</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>10616; 28226</t>
+          <t>11277; 29341</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>25450; 49412</t>
+          <t>24545; 48496</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>31053; 58575</t>
+          <t>30601; 57381</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>44103; 65273</t>
+          <t>43611; 65613</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>738000; 835283</t>
+          <t>738252; 831122</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>819942; 925148</t>
+          <t>823239; 931331</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>683521; 780111</t>
+          <t>692520; 783155</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>466080; 677159</t>
+          <t>462873; 672309</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>825485; 928483</t>
+          <t>832173; 926843</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>850603; 961140</t>
+          <t>862414; 965794</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>707216; 799085</t>
+          <t>707993; 804134</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>518144; 714249</t>
+          <t>520003; 711757</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1595910; 1728616</t>
+          <t>1600758; 1731109</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1714774; 1865452</t>
+          <t>1714290; 1857413</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1419039; 1551376</t>
+          <t>1416417; 1558872</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1057834; 1341274</t>
+          <t>1075093; 1342961</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C03-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P19C03-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,72%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>31,26; 41,58</t>
+          <t>31,55; 41,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29,32; 39,32</t>
+          <t>28,92; 38,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23,9; 33,98</t>
+          <t>24,23; 33,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14,12; 29,81</t>
+          <t>16,19; 30,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,7; 37,82</t>
+          <t>28,45; 37,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,86; 34,2</t>
+          <t>24,67; 34,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,1; 29,97</t>
+          <t>20,62; 29,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,16; 24,32</t>
+          <t>11,18; 23,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>31,42; 38,25</t>
+          <t>31,19; 38,32</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28,17; 35,05</t>
+          <t>28,29; 35,06</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23,48; 30,18</t>
+          <t>23,75; 30,75</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,33; 24,58</t>
+          <t>15,05; 24,8</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>21,03%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>35,38; 44,22</t>
+          <t>35,9; 44,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30,16; 38,07</t>
+          <t>30,5; 38,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29,7; 38,52</t>
+          <t>30,11; 38,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,73; 28,69</t>
+          <t>17,45; 27,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,2; 44,05</t>
+          <t>35,1; 43,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,77; 37,97</t>
+          <t>29,84; 38,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,43; 34,6</t>
+          <t>26,13; 34,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,32; 21,57</t>
+          <t>16,54; 24,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>36,63; 42,74</t>
+          <t>36,76; 42,54</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31,3; 36,81</t>
+          <t>31,05; 37,01</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29,09; 35,0</t>
+          <t>29,32; 35,42</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,25; 23,34</t>
+          <t>18,18; 24,72</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,6%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>34,17; 43,38</t>
+          <t>34,77; 43,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29,64; 37,65</t>
+          <t>29,4; 37,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29,54; 38,08</t>
+          <t>29,56; 37,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,99; 26,71</t>
+          <t>18,11; 25,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>32,98; 41,46</t>
+          <t>33,22; 40,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31,95; 39,6</t>
+          <t>32,0; 39,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,29; 33,84</t>
+          <t>26,05; 33,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,42; 24,19</t>
+          <t>18,99; 24,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>35,09; 40,94</t>
+          <t>34,87; 40,82</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>31,95; 37,42</t>
+          <t>31,86; 37,3</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29,24; 34,69</t>
+          <t>29,2; 34,81</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>19,33; 24,11</t>
+          <t>19,39; 24,07</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>21,47%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>30,67; 40,42</t>
+          <t>30,77; 40,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28,56; 37,15</t>
+          <t>28,92; 37,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23,54; 31,8</t>
+          <t>23,93; 32,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,03; 22,96</t>
+          <t>18,99; 25,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>30,6; 39,85</t>
+          <t>30,74; 39,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,51; 34,6</t>
+          <t>26,51; 34,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,72; 32,7</t>
+          <t>24,65; 32,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19,63; 35,87</t>
+          <t>18,7; 23,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31,8; 38,67</t>
+          <t>31,86; 38,39</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28,92; 34,79</t>
+          <t>28,82; 34,94</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25,66; 31,3</t>
+          <t>25,21; 30,98</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,65; 24,9</t>
+          <t>19,52; 23,55</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>19,69%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,86; 25,77</t>
+          <t>16,39; 26,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>25,98; 35,63</t>
+          <t>26,03; 36,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,56; 24,96</t>
+          <t>16,1; 25,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,16; 22,63</t>
+          <t>15,74; 21,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,23; 35,32</t>
+          <t>25,44; 35,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,9; 37,2</t>
+          <t>27,23; 36,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,65; 28,9</t>
+          <t>20,27; 29,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,49; 23,71</t>
+          <t>18,3; 23,43</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22,27; 29,71</t>
+          <t>22,29; 29,79</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27,7; 35,08</t>
+          <t>27,67; 34,66</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19,91; 26,53</t>
+          <t>19,53; 25,95</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,95; 22,17</t>
+          <t>17,78; 21,84</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>14,5%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,65; 17,24</t>
+          <t>8,34; 17,34</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,23; 21,25</t>
+          <t>11,62; 21,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14,43; 24,98</t>
+          <t>13,58; 24,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10,68; 16,49</t>
+          <t>10,06; 16,34</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15,75; 25,6</t>
+          <t>16,18; 26,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,97; 24,97</t>
+          <t>16,03; 25,01</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17,22; 27,15</t>
+          <t>17,84; 27,28</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,98; 16,84</t>
+          <t>13,24; 18,54</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13,59; 20,4</t>
+          <t>13,54; 20,11</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15,35; 22,23</t>
+          <t>15,14; 21,87</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17,32; 24,64</t>
+          <t>17,3; 24,66</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,96; 15,35</t>
+          <t>12,86; 16,62</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,17; 11,02</t>
+          <t>2,22; 11,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,51; 13,14</t>
+          <t>4,53; 13,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,18; 15,41</t>
+          <t>6,59; 14,94</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,71; 10,53</t>
+          <t>5,9; 11,12</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,72; 9,33</t>
+          <t>2,74; 9,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,31; 10,08</t>
+          <t>4,22; 10,39</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,81; 18,97</t>
+          <t>7,65; 18,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,07; 9,73</t>
+          <t>6,32; 10,05</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,37; 8,76</t>
+          <t>3,21; 8,65</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5,03; 9,93</t>
+          <t>5,05; 10,0</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8,16; 15,3</t>
+          <t>8,35; 15,7</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,37; 9,59</t>
+          <t>6,65; 9,73</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>18,71%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>30,09; 33,87</t>
+          <t>30,02; 33,98</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>28,27; 31,98</t>
+          <t>28,35; 31,81</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25,99; 29,39</t>
+          <t>25,68; 29,35</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13,8; 20,05</t>
+          <t>17,63; 20,79</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>30,36; 33,81</t>
+          <t>30,17; 33,89</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,43; 30,71</t>
+          <t>27,38; 30,69</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,69; 28,04</t>
+          <t>24,67; 27,88</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>14,53; 19,89</t>
+          <t>17,27; 19,55</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>30,82; 33,32</t>
+          <t>30,61; 33,25</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28,31; 30,67</t>
+          <t>28,23; 30,71</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25,61; 28,18</t>
+          <t>25,74; 28,12</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>15,51; 19,38</t>
+          <t>17,79; 19,76</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>81833</t>
+          <t>86293</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>50110</t>
+          <t>56076</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>131943</t>
+          <t>142369</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>112340; 149436</t>
+          <t>113392; 148558</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>110911; 148738</t>
+          <t>109396; 147486</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>84340; 119900</t>
+          <t>85509; 119716</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>54125; 114305</t>
+          <t>61335; 116268</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>108001; 142311</t>
+          <t>107025; 141389</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>92229; 126879</t>
+          <t>91527; 127343</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>74262; 105480</t>
+          <t>72579; 104243</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>33861; 73808</t>
+          <t>38360; 79266</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>231178; 281391</t>
+          <t>229436; 281899</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>211067; 262580</t>
+          <t>211954; 262712</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>165467; 212684</t>
+          <t>167383; 216747</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>98413; 168890</t>
+          <t>108649; 179087</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>92292</t>
+          <t>98361</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>84982</t>
+          <t>96899</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>177273</t>
+          <t>195260</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>203688; 254613</t>
+          <t>206725; 254466</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>179848; 226996</t>
+          <t>181891; 227841</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>146448; 189915</t>
+          <t>148461; 190569</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>71338; 115439</t>
+          <t>77805; 124191</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>192777; 241262</t>
+          <t>192235; 237636</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>166339; 212200</t>
+          <t>166738; 214990</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>131303; 171843</t>
+          <t>129806; 170963</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>51585; 107789</t>
+          <t>79846; 117029</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>411506; 480156</t>
+          <t>412950; 477920</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>361545; 425188</t>
+          <t>358652; 427478</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>287890; 346398</t>
+          <t>290213; 350571</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>137547; 210555</t>
+          <t>168837; 229523</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>117448</t>
+          <t>128472</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>112481</t>
+          <t>132254</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>229929</t>
+          <t>260726</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>171478; 217731</t>
+          <t>174531; 217750</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>173624; 220524</t>
+          <t>172194; 219603</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>164775; 212426</t>
+          <t>164892; 209500</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>99294; 139681</t>
+          <t>108632; 151977</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>199034; 250245</t>
+          <t>200486; 247188</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>210684; 261171</t>
+          <t>211011; 259418</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>150653; 193911</t>
+          <t>149301; 192831</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>97970; 128657</t>
+          <t>115320; 150176</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>387894; 452612</t>
+          <t>385452; 451293</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>397833; 465935</t>
+          <t>396699; 464444</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>330701; 392371</t>
+          <t>330200; 393652</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>203866; 254333</t>
+          <t>234053; 290538</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>135098</t>
+          <t>149502</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>169470</t>
+          <t>151075</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>304567</t>
+          <t>300577</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>124132; 163587</t>
+          <t>124545; 163478</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>155014; 201663</t>
+          <t>157008; 202241</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>120614; 162921</t>
+          <t>122601; 165259</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>60669; 198129</t>
+          <t>128786; 175082</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>134375; 175023</t>
+          <t>135024; 174764</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>148861; 194272</t>
+          <t>148815; 193548</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>134673; 178156</t>
+          <t>134328; 177574</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>137526; 251296</t>
+          <t>134950; 168495</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>268411; 326369</t>
+          <t>268888; 323973</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>319389; 384156</t>
+          <t>318204; 385844</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>271343; 330903</t>
+          <t>266564; 327502</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>182092; 389367</t>
+          <t>273250; 329686</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>105855</t>
+          <t>109953</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>111830</t>
+          <t>124035</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>217686</t>
+          <t>233989</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>43186; 70181</t>
+          <t>44643; 71456</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>93855; 128738</t>
+          <t>94055; 130739</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>61443; 92589</t>
+          <t>59718; 92915</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>88334; 123677</t>
+          <t>93407; 129049</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>80510; 112703</t>
+          <t>81188; 114716</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>105103; 145342</t>
+          <t>106391; 144148</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>77786; 114397</t>
+          <t>80249; 115930</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>98706; 126581</t>
+          <t>108906; 139427</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>131728; 175724</t>
+          <t>131857; 176199</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208311; 263827</t>
+          <t>208070; 260620</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>152716; 203441</t>
+          <t>149782; 198973</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>193930; 239579</t>
+          <t>211317; 259518</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>47445</t>
+          <t>51773</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>63437</t>
+          <t>68067</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>110882</t>
+          <t>119840</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>18405; 36673</t>
+          <t>17748; 36883</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>29466; 55788</t>
+          <t>30507; 57387</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>33207; 57489</t>
+          <t>31240; 56228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>38370; 59274</t>
+          <t>40030; 64985</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>38904; 63208</t>
+          <t>39948; 64525</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>47847; 74818</t>
+          <t>48013; 74921</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>47700; 75201</t>
+          <t>49395; 75544</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>23887; 101047</t>
+          <t>56800; 79539</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>62472; 93759</t>
+          <t>62242; 92469</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>86261; 124954</t>
+          <t>85092; 122932</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>87806; 124920</t>
+          <t>87723; 125048</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>57141; 147283</t>
+          <t>106328; 137426</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>21718</t>
+          <t>24950</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>31856</t>
+          <t>35680</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>53575</t>
+          <t>60629</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2745; 13965</t>
+          <t>2808; 14053</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>8345; 24306</t>
+          <t>8379; 24593</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9095; 22659</t>
+          <t>9696; 21971</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15732; 29024</t>
+          <t>17841; 33623</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5671; 19419</t>
+          <t>5697; 20547</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13073; 30581</t>
+          <t>12812; 31518</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17793; 43218</t>
+          <t>17424; 41293</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>24805; 39761</t>
+          <t>28153; 44782</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>11277; 29341</t>
+          <t>10763; 28979</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>24545; 48496</t>
+          <t>24666; 48827</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>30601; 57381</t>
+          <t>31293; 58857</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>43611; 65613</t>
+          <t>49772; 72809</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>601689</t>
+          <t>649304</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>624166</t>
+          <t>664087</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1225855</t>
+          <t>1313391</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>738252; 831122</t>
+          <t>736551; 833872</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>823239; 931331</t>
+          <t>825376; 926135</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>692520; 783155</t>
+          <t>684125; 781855</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>462873; 672309</t>
+          <t>598651; 706277</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>832173; 926843</t>
+          <t>826844; 928824</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>862414; 965794</t>
+          <t>861046; 965161</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>707993; 804134</t>
+          <t>707403; 799371</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>520003; 711757</t>
+          <t>626031; 708473</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1600758; 1731109</t>
+          <t>1590088; 1727432</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1714290; 1857413</t>
+          <t>1709631; 1859926</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1416417; 1558872</t>
+          <t>1423747; 1555652</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1075093; 1342961</t>
+          <t>1248757; 1387336</t>
         </is>
       </c>
     </row>
